--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FFFE1B-70E5-41FD-BFA8-C9832BB0058E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CFDB57-2517-4CBF-991B-71EF519CB1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1366</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -324,7 +324,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8954" uniqueCount="2468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="2473">
   <si>
     <t>nt_total</t>
   </si>
@@ -7728,6 +7728,21 @@
   </si>
   <si>
     <t>Add formulas to check for dups</t>
+  </si>
+  <si>
+    <t>number of individuals - Orders Coleoptera, Odonata, Ephemertopera, Plecoptera and Trichoptera (COEPT)</t>
+  </si>
+  <si>
+    <t>pt_COEPT</t>
+  </si>
+  <si>
+    <t>percent (0-100) taxa - Orders Coleoptera, Odonata, Ephemertopera, Plecoptera and Trichoptera (COEPT)</t>
+  </si>
+  <si>
+    <t>New benthic metrics, Issue #153, pi_COEPT, pt_COEPT</t>
+  </si>
+  <si>
+    <t>pi_COEPT</t>
   </si>
 </sst>
 </file>
@@ -8542,7 +8557,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8571,7 +8586,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <f>MAX(A22:A301)</f>
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J5" s="42" t="s">
         <v>1995</v>
@@ -8589,7 +8604,7 @@
       </c>
       <c r="J6" s="41">
         <f>COUNTA(MetricMetadata!$H$6:$H$2015)</f>
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="M6" t="s">
         <v>2008</v>
@@ -8611,7 +8626,7 @@
       </c>
       <c r="H7">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2015,G7)</f>
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M7" t="s">
         <v>2010</v>
@@ -8723,7 +8738,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="40">
         <f>SUM(H7:H11)</f>
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="I14" t="s">
         <v>1994</v>
@@ -9651,6 +9666,14 @@
       </c>
       <c r="B132" s="61" t="s">
         <v>2467</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="23">
+        <v>46246</v>
+      </c>
+      <c r="B133" s="61" t="s">
+        <v>2471</v>
       </c>
     </row>
   </sheetData>
@@ -9723,7 +9746,7 @@
       </c>
       <c r="C1" s="10">
         <f>COUNTA($A$6:$A$4442)</f>
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D1" t="s">
         <v>2463</v>
@@ -9750,7 +9773,7 @@
       </c>
       <c r="C2" s="10" cm="1">
         <f t="array" ref="C2">COUNTA(_xlfn.UNIQUE($H$6:$H$4442&amp;"_"&amp;$A$6:$A$4442))-1</f>
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D2" t="s">
         <v>2464</v>
@@ -9776,7 +9799,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>SUBTOTAL(3,A6:A4436)</f>
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$4000,B2)</f>
@@ -44993,7 +45016,7 @@
         <v>fish_nt_grad_high</v>
       </c>
       <c r="J966" s="7">
-        <f t="shared" ref="J966:J1029" si="84">COUNTIF($I$6:$I$1115,I966)</f>
+        <f t="shared" ref="J966:J1020" si="84">COUNTIF($I$6:$I$1115,I966)</f>
         <v>1</v>
       </c>
       <c r="K966" s="1" t="str">
@@ -59032,7 +59055,7 @@
         <v>algae_nt_majorhab_mostlyplank</v>
       </c>
       <c r="J1346" s="7">
-        <f t="shared" ref="J1346:J1377" si="140">COUNTIF($I$6:$I$1115,I1346)</f>
+        <f t="shared" ref="J1346:J1364" si="140">COUNTIF($I$6:$I$1115,I1346)</f>
         <v>0</v>
       </c>
       <c r="K1346" s="1" t="s">
@@ -59470,7 +59493,7 @@
         <v>799</v>
       </c>
       <c r="I1359" s="18" t="str">
-        <f t="shared" ref="I1359:I1364" si="142">H1359&amp;"_"&amp;TRIM(A1359)</f>
+        <f t="shared" ref="I1359:I1366" si="142">H1359&amp;"_"&amp;TRIM(A1359)</f>
         <v>algae_nt_nutrient_high</v>
       </c>
       <c r="J1359" s="7">
@@ -59658,11 +59681,83 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1365" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B1365" s="7" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C1365" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1365" s="11"/>
+      <c r="E1365" s="11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F1365" s="11"/>
+      <c r="G1365" s="8"/>
+      <c r="H1365" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1365" s="18" t="str">
+        <f t="shared" si="142"/>
+        <v>bugs_pi_COEPT</v>
+      </c>
+      <c r="J1365" s="7"/>
+      <c r="K1365" s="1" t="str">
+        <f t="shared" ref="K1365:K1366" si="143">"unclassified_"&amp;H1365</f>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1365" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1365" s="7"/>
+      <c r="N1365" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1366" s="7" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B1366" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C1366" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1366" s="11"/>
+      <c r="E1366" s="11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F1366" s="11"/>
+      <c r="G1366" s="8"/>
+      <c r="H1366" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1366" s="18" t="str">
+        <f t="shared" si="142"/>
+        <v>bugs_pt_COEPT</v>
+      </c>
+      <c r="J1366" s="7"/>
+      <c r="K1366" s="1" t="str">
+        <f t="shared" si="143"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1366" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1366" s="7"/>
+      <c r="N1366" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2015" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2015" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1364" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N1366" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1004:A1011">
     <sortCondition ref="A1004:A1011"/>
   </sortState>
